--- a/erp-server/erp-server-wms/src/main/resources/excel/otherInstockError.xlsx
+++ b/erp-server/erp-server-wms/src/main/resources/excel/otherInstockError.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="27360" windowHeight="8235"/>
+    <workbookView windowWidth="27450" windowHeight="8235"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -32,6 +32,13 @@
 <sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="22" uniqueCount="22">
   <si>
     <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
       <t>*</t>
     </r>
     <r>
@@ -50,6 +57,13 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
       <t>*</t>
     </r>
     <r>
@@ -90,6 +104,13 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
       <t>*</t>
     </r>
     <r>
@@ -160,7 +181,7 @@
     <t>{.type}</t>
   </si>
   <si>
-    <t>{.billDate}</t>
+    <t>{.billDateStr}</t>
   </si>
   <si>
     <t>{.warehouseName}</t>
@@ -178,7 +199,7 @@
     <t>{.skuNo}</t>
   </si>
   <si>
-    <t>{.actualQty}</t>
+    <t>{.actualQtyStr}</t>
   </si>
   <si>
     <t>{.warehouseLocation}</t>

--- a/erp-server/erp-server-wms/src/main/resources/excel/otherInstockError.xlsx
+++ b/erp-server/erp-server-wms/src/main/resources/excel/otherInstockError.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="27450" windowHeight="8235"/>
+    <workbookView windowWidth="24960" windowHeight="9795"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -1241,11 +1241,11 @@
     </row>
   </sheetData>
   <dataValidations count="2">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="D1 D3:D1048576">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="D1 D3:D13 D14:D15 D16:D1048576">
       <formula1>"普通,退货"</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="A3:A1048576">
-      <formula1>"样品领用,KOL寄送,辅料包材,配件,报废,报损"</formula1>
+      <formula1>"样品归还,三无产品,报溢"</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
